--- a/artfynd/A 54032-2024 artfynd.xlsx
+++ b/artfynd/A 54032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121795535</v>
+        <v>121794296</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>100379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kilskogen, Upl</t>
+          <t>Kilskogen, Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663234</v>
+        <v>663225</v>
       </c>
       <c r="R2" t="n">
-        <v>6687636</v>
+        <v>6687625</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +748,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121794296</v>
+        <v>121794102</v>
       </c>
       <c r="B3" t="n">
         <v>100379</v>
@@ -830,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663225</v>
+        <v>663197</v>
       </c>
       <c r="R3" t="n">
-        <v>6687625</v>
+        <v>6687702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121794102</v>
+        <v>121795535</v>
       </c>
       <c r="B4" t="n">
-        <v>100379</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,37 +895,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilskogen, Kilskogen, Upl</t>
+          <t>Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663197</v>
+        <v>663234</v>
       </c>
       <c r="R4" t="n">
-        <v>6687702</v>
+        <v>6687636</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,9 +955,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,12 +982,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 54032-2024 artfynd.xlsx
+++ b/artfynd/A 54032-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121794296</v>
+        <v>121794170</v>
       </c>
       <c r="B2" t="n">
         <v>100379</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663225</v>
+        <v>663249</v>
       </c>
       <c r="R2" t="n">
-        <v>6687625</v>
+        <v>6687667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121795535</v>
+        <v>121794296</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>100379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,40 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilskogen, Upl</t>
+          <t>Kilskogen, Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663234</v>
+        <v>663225</v>
       </c>
       <c r="R4" t="n">
-        <v>6687636</v>
+        <v>6687625</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,19 +952,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121794170</v>
+        <v>121795535</v>
       </c>
       <c r="B5" t="n">
-        <v>100379</v>
+        <v>90693</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,37 +997,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilskogen, Kilskogen, Upl</t>
+          <t>Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663249</v>
+        <v>663234</v>
       </c>
       <c r="R5" t="n">
-        <v>6687667</v>
+        <v>6687636</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,9 +1057,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,12 +1084,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 54032-2024 artfynd.xlsx
+++ b/artfynd/A 54032-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121794170</v>
+        <v>121794102</v>
       </c>
       <c r="B2" t="n">
         <v>100379</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663249</v>
+        <v>663197</v>
       </c>
       <c r="R2" t="n">
-        <v>6687667</v>
+        <v>6687702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121794102</v>
+        <v>121795535</v>
       </c>
       <c r="B3" t="n">
-        <v>100379</v>
+        <v>90693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilskogen, Kilskogen, Upl</t>
+          <t>Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663197</v>
+        <v>663234</v>
       </c>
       <c r="R3" t="n">
-        <v>6687702</v>
+        <v>6687636</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +853,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +880,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121794296</v>
+        <v>121794170</v>
       </c>
       <c r="B4" t="n">
         <v>100379</v>
@@ -919,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663225</v>
+        <v>663249</v>
       </c>
       <c r="R4" t="n">
-        <v>6687625</v>
+        <v>6687667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795535</v>
+        <v>121794296</v>
       </c>
       <c r="B5" t="n">
-        <v>90693</v>
+        <v>100379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,40 +1010,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilskogen, Upl</t>
+          <t>Kilskogen, Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663234</v>
+        <v>663225</v>
       </c>
       <c r="R5" t="n">
-        <v>6687636</v>
+        <v>6687625</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,19 +1067,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,12 +1084,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 54032-2024 artfynd.xlsx
+++ b/artfynd/A 54032-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121794102</v>
+        <v>121794170</v>
       </c>
       <c r="B2" t="n">
         <v>100379</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663197</v>
+        <v>663249</v>
       </c>
       <c r="R2" t="n">
-        <v>6687702</v>
+        <v>6687667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121795535</v>
+        <v>121794296</v>
       </c>
       <c r="B3" t="n">
-        <v>90693</v>
+        <v>100379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,40 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilskogen, Upl</t>
+          <t>Kilskogen, Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663234</v>
+        <v>663225</v>
       </c>
       <c r="R3" t="n">
-        <v>6687636</v>
+        <v>6687625</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,19 +850,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121794170</v>
+        <v>121795535</v>
       </c>
       <c r="B4" t="n">
-        <v>100379</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,37 +895,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilskogen, Kilskogen, Upl</t>
+          <t>Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663249</v>
+        <v>663234</v>
       </c>
       <c r="R4" t="n">
-        <v>6687667</v>
+        <v>6687636</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,9 +955,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,19 +982,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121794296</v>
+        <v>121794102</v>
       </c>
       <c r="B5" t="n">
         <v>100379</v>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663225</v>
+        <v>663197</v>
       </c>
       <c r="R5" t="n">
-        <v>6687625</v>
+        <v>6687702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 54032-2024 artfynd.xlsx
+++ b/artfynd/A 54032-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121794170</v>
+        <v>121794296</v>
       </c>
       <c r="B2" t="n">
         <v>100379</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663249</v>
+        <v>663225</v>
       </c>
       <c r="R2" t="n">
-        <v>6687667</v>
+        <v>6687625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121794296</v>
+        <v>121794170</v>
       </c>
       <c r="B3" t="n">
         <v>100379</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663225</v>
+        <v>663249</v>
       </c>
       <c r="R3" t="n">
-        <v>6687625</v>
+        <v>6687667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54032-2024 artfynd.xlsx
+++ b/artfynd/A 54032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121794296</v>
+        <v>121794170</v>
       </c>
       <c r="B2" t="n">
-        <v>100379</v>
+        <v>100397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663225</v>
+        <v>663249</v>
       </c>
       <c r="R2" t="n">
-        <v>6687625</v>
+        <v>6687667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121794170</v>
+        <v>121795535</v>
       </c>
       <c r="B3" t="n">
-        <v>100379</v>
+        <v>90707</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilskogen, Kilskogen, Upl</t>
+          <t>Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663249</v>
+        <v>663234</v>
       </c>
       <c r="R3" t="n">
-        <v>6687667</v>
+        <v>6687636</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +853,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +880,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121795535</v>
+        <v>121794102</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>100397</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,40 +908,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilskogen, Upl</t>
+          <t>Kilskogen, Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663234</v>
+        <v>663197</v>
       </c>
       <c r="R4" t="n">
-        <v>6687636</v>
+        <v>6687702</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,19 +965,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,22 +982,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121794102</v>
+        <v>121794296</v>
       </c>
       <c r="B5" t="n">
-        <v>100379</v>
+        <v>100397</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663197</v>
+        <v>663225</v>
       </c>
       <c r="R5" t="n">
-        <v>6687702</v>
+        <v>6687625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 54032-2024 artfynd.xlsx
+++ b/artfynd/A 54032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121794170</v>
+        <v>121794102</v>
       </c>
       <c r="B2" t="n">
-        <v>100397</v>
+        <v>100399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663249</v>
+        <v>663197</v>
       </c>
       <c r="R2" t="n">
-        <v>6687667</v>
+        <v>6687702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121795535</v>
+        <v>121794170</v>
       </c>
       <c r="B3" t="n">
-        <v>90707</v>
+        <v>100399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,40 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilskogen, Upl</t>
+          <t>Kilskogen, Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663234</v>
+        <v>663249</v>
       </c>
       <c r="R3" t="n">
-        <v>6687636</v>
+        <v>6687667</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,19 +850,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121794102</v>
+        <v>121794296</v>
       </c>
       <c r="B4" t="n">
-        <v>100397</v>
+        <v>100399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663197</v>
+        <v>663225</v>
       </c>
       <c r="R4" t="n">
-        <v>6687702</v>
+        <v>6687625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121794296</v>
+        <v>121795535</v>
       </c>
       <c r="B5" t="n">
-        <v>100397</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,37 +997,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilskogen, Kilskogen, Upl</t>
+          <t>Kilskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663225</v>
+        <v>663234</v>
       </c>
       <c r="R5" t="n">
-        <v>6687625</v>
+        <v>6687636</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,9 +1057,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,12 +1084,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
